--- a/salidas/COU-BIO-agregado-2018-2022.xlsx
+++ b/salidas/COU-BIO-agregado-2018-2022.xlsx
@@ -1006,7 +1006,7 @@
         <v>-0.03947164</v>
       </c>
       <c r="S9" s="22" t="n">
-        <v>512.315619781203</v>
+        <v>512.315619781202</v>
       </c>
       <c r="T9" s="31" t="n">
         <v>3660.41107115722</v>
@@ -1162,7 +1162,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3" t="n">
-        <v>6861.39308799011</v>
+        <v>6861.3930879901</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>-16490.1032512523</v>
       </c>
       <c r="T18" s="30" t="n">
-        <v>-0.00000000000110489395410696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1548,7 +1548,7 @@
         <v>434.03202083422</v>
       </c>
       <c r="K19" s="21" t="n">
-        <v>43631.8084999281</v>
+        <v>43631.8084999282</v>
       </c>
       <c r="L19" s="17"/>
       <c r="M19" s="3"/>
@@ -1560,7 +1560,7 @@
         <v>-1343.669599</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>665.577554867841</v>
+        <v>665.57755486784</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>-141.32012154</v>
@@ -1884,7 +1884,7 @@
         <v>3763.38525669806</v>
       </c>
       <c r="K25" s="23" t="n">
-        <v>85154.7848444097</v>
+        <v>85154.7848444098</v>
       </c>
       <c r="L25" s="19" t="n">
         <v>0</v>
@@ -1908,10 +1908,10 @@
         <v>-328.3007808</v>
       </c>
       <c r="S25" s="23" t="n">
-        <v>0.00000000000432009983342141</v>
+        <v>0.00000000000363797880709171</v>
       </c>
       <c r="T25" s="32" t="n">
-        <v>134439.197725154</v>
+        <v>134439.197725155</v>
       </c>
     </row>
     <row r="26">
@@ -1980,13 +1980,13 @@
         <v>29</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>358.830701905863</v>
+        <v>358.830701905864</v>
       </c>
       <c r="F27" s="21" t="n">
         <v>713.679262694421</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>75.8630246348444</v>
+        <v>75.8630246348443</v>
       </c>
       <c r="H27" s="21" t="n">
         <v>882.792120174038</v>
@@ -2001,7 +2001,7 @@
         <v>849.66360272462</v>
       </c>
       <c r="L27" s="17" t="n">
-        <v>6285.72985378387</v>
+        <v>6285.72985378386</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>81.8095299742963</v>
@@ -2454,16 +2454,16 @@
         <v>376.619376173028</v>
       </c>
       <c r="G36" s="17" t="n">
-        <v>73.3268121230659</v>
+        <v>73.326812123066</v>
       </c>
       <c r="H36" s="21" t="n">
         <v>517.529539151324</v>
       </c>
       <c r="I36" s="17" t="n">
-        <v>359.577008311918</v>
+        <v>359.577008311917</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>548.523110799928</v>
+        <v>548.523110799929</v>
       </c>
       <c r="K36" s="21" t="n">
         <v>14137.2497313879</v>
@@ -2781,7 +2781,7 @@
         <v>28456.3074937622</v>
       </c>
       <c r="L42" s="19" t="n">
-        <v>40549.8681522449</v>
+        <v>40549.868152245</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>27733.7742098749</v>
@@ -2851,7 +2851,7 @@
       <c r="R43" s="7"/>
       <c r="S43" s="23"/>
       <c r="T43" s="32" t="n">
-        <v>65017.1692473787</v>
+        <v>65017.1692473788</v>
       </c>
     </row>
   </sheetData>
@@ -3024,7 +3024,7 @@
         <v>-0.9347438</v>
       </c>
       <c r="S9" s="41" t="n">
-        <v>554.584641415721</v>
+        <v>554.58464141572</v>
       </c>
       <c r="T9" s="44" t="n">
         <v>3764.45005115775</v>
@@ -3139,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="43" t="n">
-        <v>37.3099757268553</v>
+        <v>37.3099757268554</v>
       </c>
     </row>
     <row r="12">
@@ -3168,7 +3168,7 @@
         <v>0.46569953662783</v>
       </c>
       <c r="I12" s="37" t="n">
-        <v>0.00114970819730209</v>
+        <v>0.0011497081973021</v>
       </c>
       <c r="J12" s="34" t="n">
         <v>59.3980585616472</v>
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>90.3805834720559</v>
+        <v>90.380583472056</v>
       </c>
       <c r="I13" s="37" t="n">
         <v>8.956133</v>
@@ -3531,7 +3531,7 @@
         <v>-16609.7979607234</v>
       </c>
       <c r="T18" s="43" t="n">
-        <v>0.000000000000801136934569513</v>
+        <v>-0.00000000000363797880709171</v>
       </c>
     </row>
     <row r="19">
@@ -3566,7 +3566,7 @@
         <v>437.192621294171</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>45091.8388271271</v>
+        <v>45091.838827127</v>
       </c>
       <c r="L19" s="37"/>
       <c r="M19" s="34"/>
@@ -3887,7 +3887,7 @@
         <v>2782.01078330859</v>
       </c>
       <c r="F25" s="42" t="n">
-        <v>5197.02774671864</v>
+        <v>5197.02774671863</v>
       </c>
       <c r="G25" s="39" t="n">
         <v>757.770701432154</v>
@@ -3926,7 +3926,7 @@
         <v>-392.355118666696</v>
       </c>
       <c r="S25" s="42" t="n">
-        <v>0.000000000309682945953682</v>
+        <v>0.000000000309228198602796</v>
       </c>
       <c r="T25" s="45" t="n">
         <v>135253.262094431</v>
@@ -3967,7 +3967,7 @@
         <v>99.1216052830558</v>
       </c>
       <c r="L26" s="38" t="n">
-        <v>914.123610389129</v>
+        <v>914.12361038913</v>
       </c>
       <c r="M26" s="35" t="n">
         <v>202.229787223053</v>
@@ -4001,7 +4001,7 @@
         <v>352.359095957921</v>
       </c>
       <c r="F27" s="40" t="n">
-        <v>676.85383909533</v>
+        <v>676.853839095331</v>
       </c>
       <c r="G27" s="37" t="n">
         <v>74.8488525462099</v>
@@ -4016,10 +4016,10 @@
         <v>35.4672356377815</v>
       </c>
       <c r="K27" s="40" t="n">
-        <v>865.670566008003</v>
+        <v>865.670566008002</v>
       </c>
       <c r="L27" s="37" t="n">
-        <v>6444.44576285975</v>
+        <v>6444.44576285974</v>
       </c>
       <c r="M27" s="34" t="n">
         <v>119.174959980984</v>
@@ -4163,7 +4163,7 @@
         <v>9.53816442060106</v>
       </c>
       <c r="H30" s="40" t="n">
-        <v>86.336851098986</v>
+        <v>86.3368510989861</v>
       </c>
       <c r="I30" s="37" t="n">
         <v>14.6453406819188</v>
@@ -4328,7 +4328,7 @@
         <v>852.412674297569</v>
       </c>
       <c r="K33" s="40" t="n">
-        <v>8036.02120828862</v>
+        <v>8036.02120828863</v>
       </c>
       <c r="L33" s="37" t="n">
         <v>4765.61654143686</v>
@@ -4472,16 +4472,16 @@
         <v>368.861455307783</v>
       </c>
       <c r="G36" s="37" t="n">
-        <v>72.7602783410528</v>
+        <v>72.7602783410529</v>
       </c>
       <c r="H36" s="40" t="n">
-        <v>550.462081349643</v>
+        <v>550.462081349642</v>
       </c>
       <c r="I36" s="37" t="n">
         <v>357.583292699706</v>
       </c>
       <c r="J36" s="34" t="n">
-        <v>531.597383209176</v>
+        <v>531.597383209177</v>
       </c>
       <c r="K36" s="40" t="n">
         <v>14188.2615247378</v>
@@ -4846,7 +4846,7 @@
         <v>1913.62241689552</v>
       </c>
       <c r="G43" s="39" t="n">
-        <v>339.435527041129</v>
+        <v>339.43552704113</v>
       </c>
       <c r="H43" s="42" t="n">
         <v>1983.12643356304</v>
@@ -5434,7 +5434,7 @@
         <v>-75.56648655</v>
       </c>
       <c r="S16" s="52" t="n">
-        <v>4713.49866776781</v>
+        <v>4713.49866776782</v>
       </c>
       <c r="T16" s="55" t="n">
         <v>15859.2810683327</v>
@@ -5549,7 +5549,7 @@
         <v>-13390.1507550036</v>
       </c>
       <c r="T18" s="55" t="n">
-        <v>-0.00000000000339017702799538</v>
+        <v>0.00000000000181898940354586</v>
       </c>
     </row>
     <row r="19">
@@ -5590,7 +5590,7 @@
       <c r="M19" s="46"/>
       <c r="N19" s="46"/>
       <c r="O19" s="46" t="n">
-        <v>2629.48186808337</v>
+        <v>2629.48186808338</v>
       </c>
       <c r="P19" s="46" t="n">
         <v>-928.990744999997</v>
@@ -5944,7 +5944,7 @@
         <v>-316.88702409</v>
       </c>
       <c r="S25" s="54" t="n">
-        <v>0.0000000000022992718839987</v>
+        <v>0.0000000000037132519281613</v>
       </c>
       <c r="T25" s="57" t="n">
         <v>101665.729616931</v>
@@ -5982,7 +5982,7 @@
         <v>0.780971881784538</v>
       </c>
       <c r="K26" s="53" t="n">
-        <v>63.2736524883953</v>
+        <v>63.2736524883952</v>
       </c>
       <c r="L26" s="50" t="n">
         <v>1078.66517601986</v>
@@ -6019,7 +6019,7 @@
         <v>335.477196219126</v>
       </c>
       <c r="F27" s="52" t="n">
-        <v>573.858867038423</v>
+        <v>573.858867038424</v>
       </c>
       <c r="G27" s="49" t="n">
         <v>59.395869338925</v>
@@ -6034,7 +6034,7 @@
         <v>21.7850346750712</v>
       </c>
       <c r="K27" s="52" t="n">
-        <v>559.583467884623</v>
+        <v>559.583467884624</v>
       </c>
       <c r="L27" s="49" t="n">
         <v>6594.45136661175</v>
@@ -6120,7 +6120,7 @@
         <v>29</v>
       </c>
       <c r="E29" s="49" t="n">
-        <v>159.269629612009</v>
+        <v>159.26962961201</v>
       </c>
       <c r="F29" s="52" t="n">
         <v>36.2601175610238</v>
@@ -6129,7 +6129,7 @@
         <v>68.2661508294115</v>
       </c>
       <c r="H29" s="52" t="n">
-        <v>8.67275327074497</v>
+        <v>8.67275327074498</v>
       </c>
       <c r="I29" s="49" t="n">
         <v>2.42244705994195</v>
@@ -6343,7 +6343,7 @@
         <v>272.230625354248</v>
       </c>
       <c r="J33" s="46" t="n">
-        <v>470.739481676227</v>
+        <v>470.739481676226</v>
       </c>
       <c r="K33" s="52" t="n">
         <v>3987.5845558679</v>
@@ -6876,7 +6876,7 @@
         <v>1022.38591929961</v>
       </c>
       <c r="K43" s="54" t="n">
-        <v>48278.8248615675</v>
+        <v>48278.8248615676</v>
       </c>
       <c r="L43" s="51"/>
       <c r="M43" s="48"/>
@@ -7319,7 +7319,7 @@
         <v>60</v>
       </c>
       <c r="J14" s="58" t="n">
-        <v>0.00695612747011719</v>
+        <v>0.0069561274701172</v>
       </c>
       <c r="K14" s="64" t="n">
         <v>178.495944885661</v>
@@ -7567,7 +7567,7 @@
         <v>-16119.6774144409</v>
       </c>
       <c r="T18" s="67" t="n">
-        <v>-0.0000000000014388490399142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -7623,7 +7623,7 @@
         <v>0.00000000430629365499868</v>
       </c>
       <c r="T19" s="67" t="n">
-        <v>48645.6923740339</v>
+        <v>48645.6923740338</v>
       </c>
     </row>
     <row r="20">
@@ -7938,7 +7938,7 @@
         <v>2410.17986429528</v>
       </c>
       <c r="K25" s="66" t="n">
-        <v>80159.2595049783</v>
+        <v>80159.2595049782</v>
       </c>
       <c r="L25" s="63" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
         <v>25965.6461165008</v>
       </c>
       <c r="P25" s="60" t="n">
-        <v>0</v>
+        <v>0.000000000000227373675443232</v>
       </c>
       <c r="Q25" s="60" t="n">
         <v>2122.8410982923</v>
@@ -7962,7 +7962,7 @@
         <v>-318.769817005183</v>
       </c>
       <c r="S25" s="66" t="n">
-        <v>-0.0000000000029117819266844</v>
+        <v>-0.000000000002892242001451</v>
       </c>
       <c r="T25" s="69" t="n">
         <v>125927.242137207</v>
@@ -8000,7 +8000,7 @@
         <v>0.808057555591546</v>
       </c>
       <c r="K26" s="65" t="n">
-        <v>90.2177561013301</v>
+        <v>90.21775610133</v>
       </c>
       <c r="L26" s="62" t="n">
         <v>1153.71564427688</v>
@@ -8052,7 +8052,7 @@
         <v>27.4793486574947</v>
       </c>
       <c r="K27" s="64" t="n">
-        <v>704.919853115367</v>
+        <v>704.919853115368</v>
       </c>
       <c r="L27" s="61" t="n">
         <v>7401.53472232054</v>
@@ -8092,7 +8092,7 @@
         <v>0.0497922169795624</v>
       </c>
       <c r="G28" s="61" t="n">
-        <v>0.0457982482717049</v>
+        <v>0.045798248271705</v>
       </c>
       <c r="H28" s="64" t="n">
         <v>0</v>
@@ -8355,7 +8355,7 @@
         <v>171.500738119341</v>
       </c>
       <c r="H33" s="64" t="n">
-        <v>49.3543383127343</v>
+        <v>49.3543383127342</v>
       </c>
       <c r="I33" s="61" t="n">
         <v>527.229773629626</v>
@@ -8401,7 +8401,7 @@
         <v>25.0240182804415</v>
       </c>
       <c r="F34" s="64" t="n">
-        <v>30.5199454761683</v>
+        <v>30.5199454761682</v>
       </c>
       <c r="G34" s="61" t="n">
         <v>5.52399645721873</v>
@@ -8502,7 +8502,7 @@
         <v>30</v>
       </c>
       <c r="E36" s="61" t="n">
-        <v>224.575140928981</v>
+        <v>224.575140928982</v>
       </c>
       <c r="F36" s="64" t="n">
         <v>367.056019918424</v>
@@ -8523,7 +8523,7 @@
         <v>13301.9129392664</v>
       </c>
       <c r="L36" s="61" t="n">
-        <v>24444.3159224656</v>
+        <v>24444.3159224657</v>
       </c>
       <c r="M36" s="58" t="n">
         <v>191.654745942925</v>
@@ -9275,7 +9275,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="76" t="n">
-        <v>88.1776832759127</v>
+        <v>88.1776832759128</v>
       </c>
       <c r="I13" s="73" t="n">
         <v>2</v>
@@ -9585,7 +9585,7 @@
         <v>-20099.6424905171</v>
       </c>
       <c r="T18" s="79" t="n">
-        <v>0.00000000000749622586226906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -9605,7 +9605,7 @@
         <v>2.61742611032783</v>
       </c>
       <c r="F19" s="76" t="n">
-        <v>48.7095260185909</v>
+        <v>48.709526018591</v>
       </c>
       <c r="G19" s="73" t="n">
         <v>24.0787881071626</v>
@@ -9620,7 +9620,7 @@
         <v>353.271456324828</v>
       </c>
       <c r="K19" s="76" t="n">
-        <v>50724.2370027736</v>
+        <v>50724.2370027737</v>
       </c>
       <c r="L19" s="73"/>
       <c r="M19" s="70"/>
@@ -9632,7 +9632,7 @@
         <v>-2363.09618</v>
       </c>
       <c r="Q19" s="70" t="n">
-        <v>670.043835822055</v>
+        <v>670.043835822056</v>
       </c>
       <c r="R19" s="70" t="n">
         <v>-219.16702435</v>
@@ -9941,10 +9941,10 @@
         <v>3287.01629194777</v>
       </c>
       <c r="F25" s="78" t="n">
-        <v>5920.73655930226</v>
+        <v>5920.73655930227</v>
       </c>
       <c r="G25" s="75" t="n">
-        <v>873.203690516486</v>
+        <v>873.203690516487</v>
       </c>
       <c r="H25" s="78" t="n">
         <v>3122.50695931149</v>
@@ -9980,7 +9980,7 @@
         <v>-425.42049333</v>
       </c>
       <c r="S25" s="78" t="n">
-        <v>-0.0000000000272496469833072</v>
+        <v>-0.0000000000236756170224339</v>
       </c>
       <c r="T25" s="81" t="n">
         <v>149752.355953791</v>
@@ -10070,7 +10070,7 @@
         <v>30.0372582328009</v>
       </c>
       <c r="K27" s="76" t="n">
-        <v>839.383609107555</v>
+        <v>839.383609107556</v>
       </c>
       <c r="L27" s="73" t="n">
         <v>8171.83061759262</v>
@@ -10214,7 +10214,7 @@
         <v>66.9666782368693</v>
       </c>
       <c r="G30" s="73" t="n">
-        <v>9.67960488941932</v>
+        <v>9.67960488941931</v>
       </c>
       <c r="H30" s="76" t="n">
         <v>58.4218051977547</v>
@@ -10226,7 +10226,7 @@
         <v>70.5568117569135</v>
       </c>
       <c r="K30" s="76" t="n">
-        <v>1185.05183680887</v>
+        <v>1185.05183680886</v>
       </c>
       <c r="L30" s="73" t="n">
         <v>751.341384253544</v>
@@ -10336,7 +10336,7 @@
         <v>17.8217829955858</v>
       </c>
       <c r="M32" s="70" t="n">
-        <v>-0.00444546200000005</v>
+        <v>-0.00444546200000004</v>
       </c>
       <c r="N32" s="70" t="n">
         <v>3153.19881316456</v>
@@ -10379,7 +10379,7 @@
         <v>527.840099317398</v>
       </c>
       <c r="J33" s="70" t="n">
-        <v>661.305573155925</v>
+        <v>661.305573155926</v>
       </c>
       <c r="K33" s="76" t="n">
         <v>8085.45672224785</v>
@@ -10523,10 +10523,10 @@
         <v>232.707937381483</v>
       </c>
       <c r="F36" s="76" t="n">
-        <v>381.812183373871</v>
+        <v>381.812183373872</v>
       </c>
       <c r="G36" s="73" t="n">
-        <v>75.4316655906561</v>
+        <v>75.431665590656</v>
       </c>
       <c r="H36" s="76" t="n">
         <v>477.598781080885</v>
@@ -10555,7 +10555,7 @@
       <c r="R36" s="70"/>
       <c r="S36" s="76"/>
       <c r="T36" s="79" t="n">
-        <v>54668.1768693239</v>
+        <v>54668.1768693238</v>
       </c>
     </row>
     <row r="37">
@@ -10853,7 +10853,7 @@
         <v>29010.6669996973</v>
       </c>
       <c r="L42" s="75" t="n">
-        <v>46911.2532369015</v>
+        <v>46911.2532369016</v>
       </c>
       <c r="M42" s="72" t="n">
         <v>27421.5766922004</v>
@@ -10912,7 +10912,7 @@
         <v>1317.41942514213</v>
       </c>
       <c r="K43" s="78" t="n">
-        <v>63978.2630941242</v>
+        <v>63978.2630941241</v>
       </c>
       <c r="L43" s="75"/>
       <c r="M43" s="72"/>
